--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_PROGRES PENDATAAN.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_PROGRES PENDATAAN.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,222 +429,222 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Nama PCL</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Email PCL</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nama PML</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Email PML</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>nama_kec</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>koseka</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha &amp; Keluarga</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Responden Didata</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Persentase Responden Didata</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Responden Sedang Didata (DRAFT)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Persentase Responden Sedang Didata (DRAFT)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Diff_Target_Pencacah</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pencacah</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Diff_Target_Pengawas</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pengawas</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>DRAFT</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>APPROVED BY Pengawas</t>
         </is>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_PROGRES PENDATAAN.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_PROGRES PENDATAAN.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,226 +413,226 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR132"/>
+  <dimension ref="A1:AR133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Nama PCL</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Email PCL</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nama PML</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Email PML</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>nama_kec</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>koseka</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha &amp; Keluarga</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Jumlah Responden Didata</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Persentase Responden Didata</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Jumlah Responden Sedang Didata (DRAFT)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Persentase Responden Sedang Didata (DRAFT)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Diff_Target_Pencacah</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pencacah</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Diff_Target_Pengawas</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pengawas</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>DRAFT</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>APPROVED BY Pengawas</t>
         </is>
@@ -781,19 +769,19 @@
         <v>50</v>
       </c>
       <c r="AN2" t="n">
-        <v>364</v>
+        <v>64</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AP2" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>4</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3">
@@ -1073,7 +1061,7 @@
         <v>60</v>
       </c>
       <c r="AN4" t="n">
-        <v>363</v>
+        <v>94</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1085,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5">
@@ -1219,7 +1207,7 @@
         <v>180</v>
       </c>
       <c r="AN5" t="n">
-        <v>384</v>
+        <v>184</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1228,10 +1216,10 @@
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6">
@@ -1365,7 +1353,7 @@
         <v>90</v>
       </c>
       <c r="AN6" t="n">
-        <v>354</v>
+        <v>166</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1377,7 +1365,7 @@
         <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7">
@@ -1511,19 +1499,19 @@
         <v>30</v>
       </c>
       <c r="AN7" t="n">
-        <v>336</v>
+        <v>27</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AQ7" t="n">
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8">
@@ -1657,19 +1645,19 @@
         <v>60</v>
       </c>
       <c r="AN8" t="n">
-        <v>304</v>
+        <v>85</v>
       </c>
       <c r="AO8" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AP8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
         <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9">
@@ -1803,19 +1791,19 @@
         <v>-50</v>
       </c>
       <c r="AN9" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
         <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1949,19 +1937,19 @@
         <v>150</v>
       </c>
       <c r="AN10" t="n">
-        <v>324</v>
+        <v>141</v>
       </c>
       <c r="AO10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -2095,19 +2083,19 @@
         <v>140</v>
       </c>
       <c r="AN11" t="n">
-        <v>373</v>
+        <v>142</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>2</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12">
@@ -2241,19 +2229,19 @@
         <v>30</v>
       </c>
       <c r="AN12" t="n">
-        <v>383</v>
+        <v>104</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
         <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13">
@@ -2387,19 +2375,19 @@
         <v>100</v>
       </c>
       <c r="AN13" t="n">
-        <v>373</v>
+        <v>75</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AQ13" t="n">
         <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14">
@@ -2533,19 +2521,19 @@
         <v>250</v>
       </c>
       <c r="AN14" t="n">
-        <v>364</v>
+        <v>74</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AP14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>3</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15">
@@ -2679,19 +2667,19 @@
         <v>140</v>
       </c>
       <c r="AN15" t="n">
-        <v>324</v>
+        <v>156</v>
       </c>
       <c r="AO15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AP15" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16">
@@ -2825,19 +2813,19 @@
         <v>170</v>
       </c>
       <c r="AN16" t="n">
-        <v>288</v>
+        <v>40</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17">
@@ -2872,13 +2860,13 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3880</v>
+        <v>4190</v>
       </c>
       <c r="H17" t="n">
-        <v>4340</v>
+        <v>4690</v>
       </c>
       <c r="I17" t="n">
-        <v>111.86</v>
+        <v>111.93</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2890,7 +2878,7 @@
         <v>71</v>
       </c>
       <c r="M17" t="n">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="N17" t="n">
         <v>2</v>
@@ -2911,22 +2899,22 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="W17" t="n">
-        <v>414</v>
+        <v>449</v>
       </c>
       <c r="X17" t="n">
         <v>71</v>
       </c>
       <c r="Y17" t="n">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="Z17" t="n">
         <v>2</v>
@@ -2947,43 +2935,43 @@
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="AI17" t="n">
-        <v>414</v>
+        <v>449</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-1060</v>
+        <v>-1100</v>
       </c>
       <c r="AK17" t="n">
         <v>200</v>
       </c>
       <c r="AL17" t="n">
-        <v>-1060</v>
+        <v>-1100</v>
       </c>
       <c r="AM17" t="n">
         <v>200</v>
       </c>
       <c r="AN17" t="n">
-        <v>370</v>
+        <v>71</v>
       </c>
       <c r="AO17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AR17" t="n">
-        <v>1</v>
+        <v>410</v>
       </c>
     </row>
     <row r="18">
@@ -3117,19 +3105,19 @@
         <v>50</v>
       </c>
       <c r="AN18" t="n">
-        <v>366</v>
+        <v>45</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AP18" t="n">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AR18" t="n">
-        <v>3</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19">
@@ -3263,19 +3251,19 @@
         <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>423</v>
+        <v>150</v>
       </c>
       <c r="AO19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
         <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20">
@@ -3409,19 +3397,19 @@
         <v>40</v>
       </c>
       <c r="AN20" t="n">
-        <v>284</v>
+        <v>15</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21">
@@ -3555,19 +3543,19 @@
         <v>10</v>
       </c>
       <c r="AN21" t="n">
-        <v>367</v>
+        <v>163</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AR21" t="n">
-        <v>4</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22">
@@ -3602,13 +3590,13 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>4370</v>
+        <v>3960</v>
       </c>
       <c r="H22" t="n">
-        <v>3560</v>
+        <v>3470</v>
       </c>
       <c r="I22" t="n">
-        <v>81.45999999999999</v>
+        <v>87.63</v>
       </c>
       <c r="J22" t="n">
         <v>20</v>
@@ -3617,19 +3605,19 @@
         <v>1.68</v>
       </c>
       <c r="L22" t="n">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="M22" t="n">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="N22" t="n">
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="P22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3641,31 +3629,31 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>531</v>
+        <v>488</v>
       </c>
       <c r="W22" t="n">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="X22" t="n">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="Y22" t="n">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="Z22" t="n">
         <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="AB22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3677,43 +3665,43 @@
         <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>531</v>
+        <v>488</v>
       </c>
       <c r="AI22" t="n">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="AJ22" t="n">
-        <v>-940</v>
+        <v>-920</v>
       </c>
       <c r="AK22" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AL22" t="n">
-        <v>-940</v>
+        <v>-920</v>
       </c>
       <c r="AM22" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN22" t="n">
-        <v>410</v>
+        <v>105</v>
       </c>
       <c r="AO22" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="AP22" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AQ22" t="n">
         <v>1</v>
       </c>
       <c r="AR22" t="n">
-        <v>22</v>
+        <v>299</v>
       </c>
     </row>
     <row r="23">
@@ -3847,19 +3835,19 @@
         <v>30</v>
       </c>
       <c r="AN23" t="n">
-        <v>450</v>
+        <v>141</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP23" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>354</v>
       </c>
     </row>
     <row r="24">
@@ -3993,19 +3981,19 @@
         <v>150</v>
       </c>
       <c r="AN24" t="n">
-        <v>359</v>
+        <v>137</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25">
@@ -4139,25 +4127,25 @@
         <v>140</v>
       </c>
       <c r="AN25" t="n">
-        <v>308</v>
+        <v>32</v>
       </c>
       <c r="AO25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>4</v>
+        <v>297</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>NaN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4186,34 +4174,34 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>4290</v>
+        <v>610</v>
       </c>
       <c r="H26" t="n">
-        <v>3280</v>
+        <v>700</v>
       </c>
       <c r="I26" t="n">
-        <v>76.45999999999999</v>
+        <v>114.75</v>
       </c>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>211</v>
+        <v>50</v>
       </c>
       <c r="N26" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4225,31 +4213,31 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V26" t="n">
-        <v>479</v>
+        <v>70</v>
       </c>
       <c r="W26" t="n">
-        <v>309</v>
+        <v>70</v>
       </c>
       <c r="X26" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>211</v>
+        <v>50</v>
       </c>
       <c r="Z26" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4261,43 +4249,43 @@
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="AG26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH26" t="n">
-        <v>479</v>
+        <v>70</v>
       </c>
       <c r="AI26" t="n">
-        <v>307</v>
+        <v>70</v>
       </c>
       <c r="AJ26" t="n">
-        <v>-500</v>
+        <v>-90</v>
       </c>
       <c r="AK26" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>-500</v>
+        <v>-90</v>
       </c>
       <c r="AM26" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>419</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
@@ -4431,19 +4419,19 @@
         <v>120</v>
       </c>
       <c r="AN27" t="n">
-        <v>342</v>
+        <v>56</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AQ27" t="n">
         <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>3</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28">
@@ -4577,10 +4565,10 @@
         <v>30</v>
       </c>
       <c r="AN28" t="n">
-        <v>384</v>
+        <v>109</v>
       </c>
       <c r="AO28" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="AP28" t="n">
         <v>0</v>
@@ -4589,7 +4577,7 @@
         <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
     </row>
     <row r="29">
@@ -4723,19 +4711,19 @@
         <v>190</v>
       </c>
       <c r="AN29" t="n">
-        <v>357</v>
+        <v>133</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
     </row>
     <row r="30">
@@ -4869,19 +4857,19 @@
         <v>70</v>
       </c>
       <c r="AN30" t="n">
-        <v>457</v>
+        <v>139</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AQ30" t="n">
         <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31">
@@ -5015,19 +5003,19 @@
         <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>315</v>
+        <v>3</v>
       </c>
       <c r="AO31" t="n">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="AP31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AQ31" t="n">
         <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32">
@@ -5161,19 +5149,19 @@
         <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>308</v>
+        <v>134</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33">
@@ -5307,19 +5295,19 @@
         <v>240</v>
       </c>
       <c r="AN33" t="n">
-        <v>365</v>
+        <v>156</v>
       </c>
       <c r="AO33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AP33" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34">
@@ -5453,19 +5441,19 @@
         <v>140</v>
       </c>
       <c r="AN34" t="n">
-        <v>410</v>
+        <v>126</v>
       </c>
       <c r="AO34" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AP34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>425</v>
       </c>
     </row>
     <row r="35">
@@ -5599,19 +5587,19 @@
         <v>190</v>
       </c>
       <c r="AN35" t="n">
-        <v>303</v>
+        <v>131</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AQ35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36">
@@ -5745,19 +5733,19 @@
         <v>30</v>
       </c>
       <c r="AN36" t="n">
-        <v>412</v>
+        <v>93</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>4</v>
+        <v>325</v>
       </c>
     </row>
     <row r="37">
@@ -5891,19 +5879,19 @@
         <v>30</v>
       </c>
       <c r="AN37" t="n">
-        <v>371</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
         <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>432</v>
       </c>
     </row>
     <row r="38">
@@ -5934,7 +5922,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6037,19 +6025,19 @@
         <v>290</v>
       </c>
       <c r="AN38" t="n">
-        <v>453</v>
+        <v>122</v>
       </c>
       <c r="AO38" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="AP38" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>296</v>
       </c>
     </row>
     <row r="39">
@@ -6080,7 +6068,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6183,19 +6171,19 @@
         <v>170</v>
       </c>
       <c r="AN39" t="n">
-        <v>445</v>
+        <v>152</v>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AP39" t="n">
         <v>4</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
     </row>
     <row r="40">
@@ -6329,19 +6317,19 @@
         <v>190</v>
       </c>
       <c r="AN40" t="n">
-        <v>379</v>
+        <v>86</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
         <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
     </row>
     <row r="41">
@@ -6475,19 +6463,19 @@
         <v>90</v>
       </c>
       <c r="AN41" t="n">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42">
@@ -6621,19 +6609,19 @@
         <v>340</v>
       </c>
       <c r="AN42" t="n">
-        <v>371</v>
+        <v>127</v>
       </c>
       <c r="AO42" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AP42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ42" t="n">
         <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43">
@@ -6767,7 +6755,7 @@
         <v>110</v>
       </c>
       <c r="AN43" t="n">
-        <v>331</v>
+        <v>42</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -6776,10 +6764,10 @@
         <v>13</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR43" t="n">
-        <v>1</v>
+        <v>319</v>
       </c>
     </row>
     <row r="44">
@@ -6913,7 +6901,7 @@
         <v>20</v>
       </c>
       <c r="AN44" t="n">
-        <v>301</v>
+        <v>12</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -6922,218 +6910,218 @@
         <v>9</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR44" t="n">
-        <v>10</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Fitrianti Tadete</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>fitriantitadete68@gmail.com</t>
+          <t>fransiskapaolin@gmail.com</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Derlan Malawere</t>
+          <t>Yulianti Manambe</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>derlanmalawere92@gmail.com</t>
+          <t>anthymanambe8@gmail.com</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(100) TABUKAN UTARA</t>
+          <t>(092) TAHUNA BARAT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>3510</v>
+        <v>4330</v>
       </c>
       <c r="H45" t="n">
-        <v>3420</v>
+        <v>3270</v>
       </c>
       <c r="I45" t="n">
-        <v>97.44</v>
+        <v>75.52</v>
       </c>
       <c r="J45" t="n">
         <v>10</v>
       </c>
       <c r="K45" t="n">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="L45" t="n">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="M45" t="n">
-        <v>329</v>
+        <v>236</v>
       </c>
       <c r="N45" t="n">
         <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V45" t="n">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="W45" t="n">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="X45" t="n">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="Y45" t="n">
-        <v>329</v>
+        <v>236</v>
       </c>
       <c r="Z45" t="n">
         <v>1</v>
       </c>
       <c r="AA45" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AH45" t="n">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="AI45" t="n">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="AJ45" t="n">
-        <v>-760</v>
+        <v>-440</v>
       </c>
       <c r="AK45" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AL45" t="n">
-        <v>-760</v>
+        <v>-440</v>
       </c>
       <c r="AM45" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AN45" t="n">
-        <v>355</v>
+        <v>146</v>
       </c>
       <c r="AO45" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AR45" t="n">
-        <v>2</v>
+        <v>236</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>fransiskapaolin@gmail.com</t>
+          <t>frzfrz130293@gmail.com</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Yulianti Manambe</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>anthymanambe8@gmail.com</t>
+          <t>yanfwpadang84@gmail.com</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(092) TAHUNA BARAT</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>4330</v>
+        <v>3800</v>
       </c>
       <c r="H46" t="n">
-        <v>3270</v>
+        <v>2790</v>
       </c>
       <c r="I46" t="n">
-        <v>75.52</v>
+        <v>73.42</v>
       </c>
       <c r="J46" t="n">
         <v>10</v>
       </c>
       <c r="K46" t="n">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="L46" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="M46" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="P46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7145,31 +7133,31 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="U46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>477</v>
+        <v>433</v>
       </c>
       <c r="W46" t="n">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="X46" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="Y46" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="Z46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="AB46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7181,230 +7169,230 @@
         <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="AG46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>477</v>
+        <v>432</v>
       </c>
       <c r="AI46" t="n">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="AJ46" t="n">
-        <v>-440</v>
+        <v>-530</v>
       </c>
       <c r="AK46" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AL46" t="n">
-        <v>-440</v>
+        <v>-520</v>
       </c>
       <c r="AM46" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN46" t="n">
-        <v>434</v>
+        <v>132</v>
       </c>
       <c r="AO46" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="AP46" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AQ46" t="n">
         <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>frzfrz130293@gmail.com</t>
+          <t>geovanimonok34@gmail.com</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>B. Lenskar Diamanis</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>yanfwpadang84@gmail.com</t>
+          <t>lenskardiamaniz@gmail.com</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(080) MANGANITU</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>3800</v>
+        <v>3550</v>
       </c>
       <c r="H47" t="n">
-        <v>2790</v>
+        <v>2990</v>
       </c>
       <c r="I47" t="n">
-        <v>73.42</v>
+        <v>84.23</v>
       </c>
       <c r="J47" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="M47" t="n">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="O47" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="W47" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="X47" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="Y47" t="n">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AA47" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="AI47" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="AJ47" t="n">
-        <v>-530</v>
+        <v>-730</v>
       </c>
       <c r="AK47" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>-520</v>
+        <v>-730</v>
       </c>
       <c r="AM47" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>375</v>
+        <v>128</v>
       </c>
       <c r="AO47" t="n">
         <v>1</v>
       </c>
       <c r="AP47" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>geovanimonok34@gmail.com</t>
+          <t>ghenovhepaparaso@gmail.com</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B. Lenskar Diamanis</t>
+          <t>Ferdinand Tangkabiringan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>lenskardiamaniz@gmail.com</t>
+          <t>ferdinandtangkabiringan@gmail.com</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>(080) MANGANITU</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>3550</v>
+        <v>4100</v>
       </c>
       <c r="H48" t="n">
-        <v>2990</v>
+        <v>3890</v>
       </c>
       <c r="I48" t="n">
-        <v>84.23</v>
+        <v>94.88</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -7413,55 +7401,55 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="M48" t="n">
-        <v>218</v>
+        <v>334</v>
       </c>
       <c r="N48" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>25</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="n">
+        <v>485</v>
+      </c>
+      <c r="W48" t="n">
+        <v>364</v>
+      </c>
+      <c r="X48" t="n">
+        <v>121</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>334</v>
+      </c>
+      <c r="Z48" t="n">
         <v>4</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>42</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>428</v>
-      </c>
-      <c r="W48" t="n">
-        <v>299</v>
-      </c>
-      <c r="X48" t="n">
-        <v>128</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>218</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>35</v>
-      </c>
       <c r="AA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -7473,31 +7461,31 @@
         <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH48" t="n">
-        <v>428</v>
+        <v>485</v>
       </c>
       <c r="AI48" t="n">
-        <v>299</v>
+        <v>364</v>
       </c>
       <c r="AJ48" t="n">
-        <v>-730</v>
+        <v>-750</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AL48" t="n">
-        <v>-730</v>
+        <v>-750</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AN48" t="n">
-        <v>363</v>
+        <v>121</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -7506,51 +7494,51 @@
         <v>4</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ghenovhepaparaso@gmail.com</t>
+          <t>gracedorongpangalo11@gmail.com</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Fiane Greti Mansauda</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ferdinandtangkabiringan@gmail.com</t>
+          <t>fianemansauda89@gmail.com</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(070) TABUKAN TENGAH</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>4100</v>
+        <v>3700</v>
       </c>
       <c r="H49" t="n">
-        <v>3890</v>
+        <v>3120</v>
       </c>
       <c r="I49" t="n">
-        <v>94.88</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -7559,436 +7547,436 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="M49" t="n">
-        <v>334</v>
+        <v>242</v>
       </c>
       <c r="N49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="U49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V49" t="n">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="W49" t="n">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="X49" t="n">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="Y49" t="n">
-        <v>334</v>
+        <v>242</v>
       </c>
       <c r="Z49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AG49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH49" t="n">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="AI49" t="n">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="AJ49" t="n">
-        <v>-750</v>
+        <v>-1060</v>
       </c>
       <c r="AK49" t="n">
-        <v>250</v>
+        <v>140</v>
       </c>
       <c r="AL49" t="n">
-        <v>-750</v>
+        <v>-1060</v>
       </c>
       <c r="AM49" t="n">
-        <v>250</v>
+        <v>140</v>
       </c>
       <c r="AN49" t="n">
-        <v>411</v>
+        <v>178</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Grees Pangandaheng</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>gracedorongpangalo11@gmail.com</t>
+          <t>greispangandaheng@gmail.com</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>Novdein Arif Bongkitang</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>fianemansauda89@gmail.com</t>
+          <t>novdeinarifbongkitang@gmail.com</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(070) TABUKAN TENGAH</t>
+          <t>(050) TAMAKO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>3700</v>
+        <v>4030</v>
       </c>
       <c r="H50" t="n">
-        <v>3120</v>
+        <v>4630</v>
       </c>
       <c r="I50" t="n">
-        <v>84.31999999999999</v>
+        <v>114.89</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="L50" t="n">
-        <v>178</v>
+        <v>61</v>
       </c>
       <c r="M50" t="n">
-        <v>242</v>
+        <v>398</v>
       </c>
       <c r="N50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P50" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="U50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>476</v>
+        <v>539</v>
       </c>
       <c r="W50" t="n">
-        <v>298</v>
+        <v>460</v>
       </c>
       <c r="X50" t="n">
-        <v>178</v>
+        <v>61</v>
       </c>
       <c r="Y50" t="n">
-        <v>242</v>
+        <v>398</v>
       </c>
       <c r="Z50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AB50" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="AG50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>476</v>
+        <v>539</v>
       </c>
       <c r="AI50" t="n">
-        <v>298</v>
+        <v>460</v>
       </c>
       <c r="AJ50" t="n">
-        <v>-1060</v>
+        <v>-1360</v>
       </c>
       <c r="AK50" t="n">
-        <v>140</v>
+        <v>30</v>
       </c>
       <c r="AL50" t="n">
-        <v>-1060</v>
+        <v>-1360</v>
       </c>
       <c r="AM50" t="n">
-        <v>140</v>
+        <v>30</v>
       </c>
       <c r="AN50" t="n">
-        <v>372</v>
+        <v>61</v>
       </c>
       <c r="AO50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AP50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Grees Pangandaheng</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>greispangandaheng@gmail.com</t>
+          <t>hamendahasrita@gmail.com</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Novdein Arif Bongkitang</t>
+          <t>Novrilley Richard Mumu</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>novdeinarifbongkitang@gmail.com</t>
+          <t>novrilleymumu11@gmail.com</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(050) TAMAKO</t>
+          <t>(100) TABUKAN UTARA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>4030</v>
+        <v>3540</v>
       </c>
       <c r="H51" t="n">
-        <v>4630</v>
+        <v>4000</v>
       </c>
       <c r="I51" t="n">
-        <v>114.89</v>
+        <v>112.99</v>
       </c>
       <c r="J51" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="M51" t="n">
-        <v>398</v>
+        <v>331</v>
       </c>
       <c r="N51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O51" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>50</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" t="n">
+        <v>482</v>
+      </c>
+      <c r="W51" t="n">
+        <v>390</v>
+      </c>
+      <c r="X51" t="n">
+        <v>89</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>331</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA51" t="n">
         <v>3</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>52</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>539</v>
-      </c>
-      <c r="W51" t="n">
-        <v>460</v>
-      </c>
-      <c r="X51" t="n">
-        <v>61</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>398</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>18</v>
-      </c>
       <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>482</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>390</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>-1280</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>-1280</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>89</v>
+      </c>
+      <c r="AO51" t="n">
         <v>3</v>
       </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>52</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>539</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>460</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>-1360</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>-1360</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>30</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>395</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
       <c r="AP51" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="AQ51" t="n">
         <v>0</v>
       </c>
       <c r="AR51" t="n">
-        <v>0</v>
+        <v>331</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>hamendahasrita@gmail.com</t>
+          <t>hapitudhy@gmail.com</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Novrilley Richard Mumu</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>novrilleymumu11@gmail.com</t>
+          <t>vonnelariunaung77560@gmail.com</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(100) TABUKAN UTARA</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>3540</v>
+        <v>4330</v>
       </c>
       <c r="H52" t="n">
-        <v>4000</v>
+        <v>3590</v>
       </c>
       <c r="I52" t="n">
-        <v>112.99</v>
+        <v>82.91</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -7997,16 +7985,16 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="M52" t="n">
-        <v>331</v>
+        <v>295</v>
       </c>
       <c r="N52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
@@ -8015,34 +8003,34 @@
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="U52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="W52" t="n">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="X52" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="Y52" t="n">
-        <v>331</v>
+        <v>295</v>
       </c>
       <c r="Z52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AB52" t="n">
         <v>0</v>
@@ -8051,40 +8039,40 @@
         <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="AG52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="AI52" t="n">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="AJ52" t="n">
-        <v>-1280</v>
+        <v>-370</v>
       </c>
       <c r="AK52" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AL52" t="n">
-        <v>-1280</v>
+        <v>-370</v>
       </c>
       <c r="AM52" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AN52" t="n">
-        <v>378</v>
+        <v>104</v>
       </c>
       <c r="AO52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AP52" t="n">
         <v>0</v>
@@ -8093,28 +8081,28 @@
         <v>0</v>
       </c>
       <c r="AR52" t="n">
-        <v>0</v>
+        <v>295</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>hapitudhy@gmail.com</t>
+          <t>harilamachris23@gmail.com</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ivonne Lariunaung</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>vonnelariunaung77560@gmail.com</t>
+          <t>jeniemonok7@gmail.com</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -8128,183 +8116,183 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>4360</v>
+        <v>4130</v>
       </c>
       <c r="H53" t="n">
-        <v>3820</v>
+        <v>2850</v>
       </c>
       <c r="I53" t="n">
-        <v>87.61</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="L53" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="M53" t="n">
-        <v>341</v>
+        <v>219</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O53" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V53" t="n">
-        <v>493</v>
+        <v>452</v>
       </c>
       <c r="W53" t="n">
-        <v>382</v>
+        <v>279</v>
       </c>
       <c r="X53" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="Y53" t="n">
-        <v>341</v>
+        <v>219</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA53" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH53" t="n">
-        <v>493</v>
+        <v>452</v>
       </c>
       <c r="AI53" t="n">
-        <v>382</v>
+        <v>279</v>
       </c>
       <c r="AJ53" t="n">
-        <v>-570</v>
+        <v>-390</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AL53" t="n">
-        <v>-570</v>
+        <v>-390</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AN53" t="n">
-        <v>429</v>
+        <v>150</v>
       </c>
       <c r="AO53" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="AP53" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AR53" t="n">
-        <v>1</v>
+        <v>219</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Sintike Susanti Meling Horman</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>harilamachris23@gmail.com</t>
+          <t>hshyntike@gmail.com</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Ningsi Karendehi</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jeniemonok7@gmail.com</t>
+          <t>ningsikarendehi968@gmail.com</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>(091) TAHUNA TIMUR</t>
+          <t>(061) TABUKAN SELATAN TENGAH &amp; (062) TABUKAN SELATAN TENGGARA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Erwin &amp; Lalu</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>4040</v>
+        <v>2770</v>
       </c>
       <c r="H54" t="n">
-        <v>2070</v>
+        <v>3270</v>
       </c>
       <c r="I54" t="n">
-        <v>51.24</v>
+        <v>118.05</v>
       </c>
       <c r="J54" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="M54" t="n">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -8313,34 +8301,34 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V54" t="n">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="W54" t="n">
-        <v>201</v>
+        <v>317</v>
       </c>
       <c r="X54" t="n">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="Y54" t="n">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD54" t="n">
         <v>0</v>
@@ -8349,84 +8337,84 @@
         <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH54" t="n">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="AI54" t="n">
-        <v>201</v>
+        <v>317</v>
       </c>
       <c r="AJ54" t="n">
-        <v>-290</v>
+        <v>-1230</v>
       </c>
       <c r="AK54" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AL54" t="n">
-        <v>-290</v>
+        <v>-1230</v>
       </c>
       <c r="AM54" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AN54" t="n">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="AO54" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR54" t="n">
-        <v>2</v>
+        <v>235</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sintike Susanti Meling Horman</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>hshyntike@gmail.com</t>
+          <t>igirisatia5@gmail.com</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ningsi Karendehi</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ningsikarendehi968@gmail.com</t>
+          <t>yanfwpadang84@gmail.com</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>(061) TABUKAN SELATAN TENGAH &amp; (062) TABUKAN SELATAN TENGGARA</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Erwin &amp; Lalu</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2770</v>
+        <v>4120</v>
       </c>
       <c r="H55" t="n">
-        <v>3270</v>
+        <v>4380</v>
       </c>
       <c r="I55" t="n">
-        <v>118.05</v>
+        <v>106.31</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -8435,22 +8423,22 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="M55" t="n">
-        <v>235</v>
+        <v>403</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -8459,34 +8447,34 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="U55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V55" t="n">
-        <v>400</v>
+        <v>636</v>
       </c>
       <c r="W55" t="n">
-        <v>317</v>
+        <v>431</v>
       </c>
       <c r="X55" t="n">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="Y55" t="n">
-        <v>235</v>
+        <v>403</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AB55" t="n">
         <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -8495,84 +8483,84 @@
         <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="AG55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH55" t="n">
-        <v>400</v>
+        <v>636</v>
       </c>
       <c r="AI55" t="n">
-        <v>317</v>
+        <v>431</v>
       </c>
       <c r="AJ55" t="n">
-        <v>-1230</v>
+        <v>-2240</v>
       </c>
       <c r="AK55" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AL55" t="n">
-        <v>-1230</v>
+        <v>-2240</v>
       </c>
       <c r="AM55" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AN55" t="n">
-        <v>279</v>
+        <v>160</v>
       </c>
       <c r="AO55" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AP55" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AQ55" t="n">
         <v>0</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>403</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>igirisatia5@gmail.com</t>
+          <t>indrydorthea@gmail.com</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>Jekir Venkil Dompas</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>yanfwpadang84@gmail.com</t>
+          <t>jekirvenkildompas@gmail.com</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(070) TABUKAN TENGAH</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>4120</v>
+        <v>3250</v>
       </c>
       <c r="H56" t="n">
-        <v>4380</v>
+        <v>3390</v>
       </c>
       <c r="I56" t="n">
-        <v>106.31</v>
+        <v>104.31</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -8581,19 +8569,19 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="M56" t="n">
-        <v>403</v>
+        <v>215</v>
       </c>
       <c r="N56" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="O56" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -8605,31 +8593,31 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="U56" t="n">
         <v>1</v>
       </c>
       <c r="V56" t="n">
-        <v>636</v>
+        <v>493</v>
       </c>
       <c r="W56" t="n">
-        <v>431</v>
+        <v>328</v>
       </c>
       <c r="X56" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="Y56" t="n">
-        <v>403</v>
+        <v>215</v>
       </c>
       <c r="Z56" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="AA56" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -8641,105 +8629,105 @@
         <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="AG56" t="n">
         <v>1</v>
       </c>
       <c r="AH56" t="n">
-        <v>636</v>
+        <v>493</v>
       </c>
       <c r="AI56" t="n">
-        <v>431</v>
+        <v>328</v>
       </c>
       <c r="AJ56" t="n">
-        <v>-2240</v>
+        <v>-1680</v>
       </c>
       <c r="AK56" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AL56" t="n">
-        <v>-2240</v>
+        <v>-1680</v>
       </c>
       <c r="AM56" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AN56" t="n">
-        <v>420</v>
+        <v>148</v>
       </c>
       <c r="AO56" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AP56" t="n">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR56" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>indrydorthea@gmail.com</t>
+          <t>iyanmaniku1@gmail.com</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jekir Venkil Dompas</t>
+          <t>Derlan Malawere</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jekirvenkildompas@gmail.com</t>
+          <t>derlanmalawere92@gmail.com</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(070) TABUKAN TENGAH</t>
+          <t>(100) TABUKAN UTARA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>3250</v>
+        <v>3510</v>
       </c>
       <c r="H57" t="n">
-        <v>3390</v>
+        <v>3420</v>
       </c>
       <c r="I57" t="n">
-        <v>104.31</v>
+        <v>97.44</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="L57" t="n">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="M57" t="n">
-        <v>215</v>
+        <v>329</v>
       </c>
       <c r="N57" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="P57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -8751,31 +8739,31 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="U57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>493</v>
+        <v>427</v>
       </c>
       <c r="W57" t="n">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="X57" t="n">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="Y57" t="n">
-        <v>215</v>
+        <v>329</v>
       </c>
       <c r="Z57" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AB57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -8787,43 +8775,43 @@
         <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="AG57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>493</v>
+        <v>427</v>
       </c>
       <c r="AI57" t="n">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AJ57" t="n">
-        <v>-1680</v>
+        <v>-760</v>
       </c>
       <c r="AK57" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="AL57" t="n">
-        <v>-1680</v>
+        <v>-760</v>
       </c>
       <c r="AM57" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="AN57" t="n">
-        <v>336</v>
+        <v>85</v>
       </c>
       <c r="AO57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AP57" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AQ57" t="n">
         <v>0</v>
       </c>
       <c r="AR57" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
     </row>
     <row r="58">
@@ -8957,19 +8945,19 @@
         <v>220</v>
       </c>
       <c r="AN58" t="n">
-        <v>363</v>
+        <v>194</v>
       </c>
       <c r="AO58" t="n">
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR58" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
     </row>
     <row r="59">
@@ -9103,19 +9091,19 @@
         <v>70</v>
       </c>
       <c r="AN59" t="n">
-        <v>383</v>
+        <v>108</v>
       </c>
       <c r="AO59" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AP59" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AQ59" t="n">
         <v>0</v>
       </c>
       <c r="AR59" t="n">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="60">
@@ -9249,19 +9237,19 @@
         <v>40</v>
       </c>
       <c r="AN60" t="n">
-        <v>377</v>
+        <v>160</v>
       </c>
       <c r="AO60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP60" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AR60" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
     </row>
     <row r="61">
@@ -9395,19 +9383,19 @@
         <v>60</v>
       </c>
       <c r="AN61" t="n">
-        <v>314</v>
+        <v>126</v>
       </c>
       <c r="AO61" t="n">
         <v>0</v>
       </c>
       <c r="AP61" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AQ61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR61" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
     </row>
     <row r="62">
@@ -9541,19 +9529,19 @@
         <v>90</v>
       </c>
       <c r="AN62" t="n">
-        <v>365</v>
+        <v>79</v>
       </c>
       <c r="AO62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP62" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="AQ62" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AR62" t="n">
-        <v>6</v>
+        <v>345</v>
       </c>
     </row>
     <row r="63">
@@ -9687,19 +9675,19 @@
         <v>210</v>
       </c>
       <c r="AN63" t="n">
-        <v>324</v>
+        <v>99</v>
       </c>
       <c r="AO63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP63" t="n">
         <v>0</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AR63" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64">
@@ -9833,19 +9821,19 @@
         <v>50</v>
       </c>
       <c r="AN64" t="n">
-        <v>440</v>
+        <v>157</v>
       </c>
       <c r="AO64" t="n">
         <v>0</v>
       </c>
       <c r="AP64" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR64" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="65">
@@ -9979,19 +9967,19 @@
         <v>70</v>
       </c>
       <c r="AN65" t="n">
-        <v>417</v>
+        <v>105</v>
       </c>
       <c r="AO65" t="n">
         <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR65" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
     </row>
     <row r="66">
@@ -10125,19 +10113,19 @@
         <v>10</v>
       </c>
       <c r="AN66" t="n">
-        <v>384</v>
+        <v>78</v>
       </c>
       <c r="AO66" t="n">
         <v>0</v>
       </c>
       <c r="AP66" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR66" t="n">
-        <v>2</v>
+        <v>316</v>
       </c>
     </row>
     <row r="67">
@@ -10271,19 +10259,19 @@
         <v>70</v>
       </c>
       <c r="AN67" t="n">
-        <v>297</v>
+        <v>100</v>
       </c>
       <c r="AO67" t="n">
         <v>0</v>
       </c>
       <c r="AP67" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AR67" t="n">
-        <v>1</v>
+        <v>185</v>
       </c>
     </row>
     <row r="68">
@@ -10417,19 +10405,19 @@
         <v>30</v>
       </c>
       <c r="AN68" t="n">
-        <v>395</v>
+        <v>21</v>
       </c>
       <c r="AO68" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AP68" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AQ68" t="n">
         <v>1</v>
       </c>
       <c r="AR68" t="n">
-        <v>8</v>
+        <v>448</v>
       </c>
     </row>
     <row r="69">
@@ -10563,19 +10551,19 @@
         <v>100</v>
       </c>
       <c r="AN69" t="n">
-        <v>317</v>
+        <v>101</v>
       </c>
       <c r="AO69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP69" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AR69" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
     </row>
     <row r="70">
@@ -10709,19 +10697,19 @@
         <v>0</v>
       </c>
       <c r="AN70" t="n">
-        <v>306</v>
+        <v>131</v>
       </c>
       <c r="AO70" t="n">
         <v>0</v>
       </c>
       <c r="AP70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ70" t="n">
         <v>0</v>
       </c>
       <c r="AR70" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
     </row>
     <row r="71">
@@ -10855,19 +10843,19 @@
         <v>180</v>
       </c>
       <c r="AN71" t="n">
-        <v>366</v>
+        <v>80</v>
       </c>
       <c r="AO71" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AP71" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AQ71" t="n">
         <v>0</v>
       </c>
       <c r="AR71" t="n">
-        <v>0</v>
+        <v>391</v>
       </c>
     </row>
     <row r="72">
@@ -11001,19 +10989,19 @@
         <v>50</v>
       </c>
       <c r="AN72" t="n">
-        <v>353</v>
+        <v>3</v>
       </c>
       <c r="AO72" t="n">
         <v>0</v>
       </c>
       <c r="AP72" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR72" t="n">
-        <v>0</v>
+        <v>492</v>
       </c>
     </row>
     <row r="73">
@@ -11147,19 +11135,19 @@
         <v>100</v>
       </c>
       <c r="AN73" t="n">
-        <v>362</v>
+        <v>105</v>
       </c>
       <c r="AO73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP73" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ73" t="n">
         <v>0</v>
       </c>
       <c r="AR73" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
     </row>
     <row r="74">
@@ -11293,10 +11281,10 @@
         <v>130</v>
       </c>
       <c r="AN74" t="n">
-        <v>398</v>
+        <v>19</v>
       </c>
       <c r="AO74" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="AP74" t="n">
         <v>0</v>
@@ -11305,7 +11293,7 @@
         <v>0</v>
       </c>
       <c r="AR74" t="n">
-        <v>0</v>
+        <v>386</v>
       </c>
     </row>
     <row r="75">
@@ -11439,19 +11427,19 @@
         <v>130</v>
       </c>
       <c r="AN75" t="n">
-        <v>359</v>
+        <v>138</v>
       </c>
       <c r="AO75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AP75" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AR75" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
     </row>
     <row r="76">
@@ -11585,19 +11573,19 @@
         <v>0</v>
       </c>
       <c r="AN76" t="n">
-        <v>357</v>
+        <v>175</v>
       </c>
       <c r="AO76" t="n">
         <v>0</v>
       </c>
       <c r="AP76" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR76" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77">
@@ -11731,19 +11719,19 @@
         <v>100</v>
       </c>
       <c r="AN77" t="n">
-        <v>386</v>
+        <v>87</v>
       </c>
       <c r="AO77" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="AP77" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR77" t="n">
-        <v>7</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78">
@@ -11877,19 +11865,19 @@
         <v>70</v>
       </c>
       <c r="AN78" t="n">
-        <v>350</v>
+        <v>114</v>
       </c>
       <c r="AO78" t="n">
         <v>0</v>
       </c>
       <c r="AP78" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR78" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="79">
@@ -12023,7 +12011,7 @@
         <v>80</v>
       </c>
       <c r="AN79" t="n">
-        <v>319</v>
+        <v>21</v>
       </c>
       <c r="AO79" t="n">
         <v>0</v>
@@ -12032,51 +12020,51 @@
         <v>6</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AR79" t="n">
-        <v>7</v>
+        <v>313</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Mery Grace Anabelia Kantohe</t>
+          <t>Aldo Jhon Mesak Bangonang</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>merykantohe979@gmail.com</t>
+          <t>mesakbangonang99@gmail.com</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>hmanabung01@gmail.com</t>
+          <t>vonnelariunaung77560@gmail.com</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>(110) KENDAHE</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>2610</v>
+        <v>3590</v>
       </c>
       <c r="H80" t="n">
-        <v>1940</v>
+        <v>1800</v>
       </c>
       <c r="I80" t="n">
-        <v>74.33</v>
+        <v>50.14</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -12085,103 +12073,103 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>95</v>
+        <v>211</v>
       </c>
       <c r="M80" t="n">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P80" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
       </c>
       <c r="V80" t="n">
-        <v>289</v>
+        <v>390</v>
       </c>
       <c r="W80" t="n">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="X80" t="n">
-        <v>95</v>
+        <v>213</v>
       </c>
       <c r="Y80" t="n">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AB80" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
       </c>
       <c r="AD80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE80" t="n">
         <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>289</v>
+        <v>390</v>
       </c>
       <c r="AI80" t="n">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="AJ80" t="n">
-        <v>-280</v>
+        <v>-310</v>
       </c>
       <c r="AK80" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AL80" t="n">
-        <v>-280</v>
+        <v>-310</v>
       </c>
       <c r="AM80" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AN80" t="n">
-        <v>263</v>
+        <v>211</v>
       </c>
       <c r="AO80" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="AP80" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR80" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="81">
@@ -12315,19 +12303,19 @@
         <v>50</v>
       </c>
       <c r="AN81" t="n">
-        <v>313</v>
+        <v>60</v>
       </c>
       <c r="AO81" t="n">
         <v>0</v>
       </c>
       <c r="AP81" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AQ81" t="n">
         <v>0</v>
       </c>
       <c r="AR81" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
     </row>
     <row r="82">
@@ -12461,19 +12449,19 @@
         <v>90</v>
       </c>
       <c r="AN82" t="n">
-        <v>385</v>
+        <v>113</v>
       </c>
       <c r="AO82" t="n">
         <v>0</v>
       </c>
       <c r="AP82" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR82" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
     </row>
     <row r="83">
@@ -12607,19 +12595,19 @@
         <v>130</v>
       </c>
       <c r="AN83" t="n">
-        <v>340</v>
+        <v>159</v>
       </c>
       <c r="AO83" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AP83" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AR83" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
     </row>
     <row r="84">
@@ -12753,19 +12741,19 @@
         <v>160</v>
       </c>
       <c r="AN84" t="n">
-        <v>378</v>
+        <v>111</v>
       </c>
       <c r="AO84" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="AP84" t="n">
         <v>0</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR84" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="85">
@@ -12899,19 +12887,19 @@
         <v>40</v>
       </c>
       <c r="AN85" t="n">
-        <v>367</v>
+        <v>126</v>
       </c>
       <c r="AO85" t="n">
         <v>0</v>
       </c>
       <c r="AP85" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR85" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
     </row>
     <row r="86">
@@ -13045,19 +13033,19 @@
         <v>110</v>
       </c>
       <c r="AN86" t="n">
-        <v>367</v>
+        <v>163</v>
       </c>
       <c r="AO86" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AP86" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR86" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
     </row>
     <row r="87">
@@ -13191,19 +13179,19 @@
         <v>170</v>
       </c>
       <c r="AN87" t="n">
-        <v>360</v>
+        <v>146</v>
       </c>
       <c r="AO87" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AP87" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AR87" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
     </row>
     <row r="88">
@@ -13337,19 +13325,19 @@
         <v>0</v>
       </c>
       <c r="AN88" t="n">
-        <v>356</v>
+        <v>70</v>
       </c>
       <c r="AO88" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AP88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR88" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
     </row>
     <row r="89">
@@ -13483,19 +13471,19 @@
         <v>240</v>
       </c>
       <c r="AN89" t="n">
-        <v>405</v>
+        <v>167</v>
       </c>
       <c r="AO89" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AP89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ89" t="n">
         <v>2</v>
       </c>
-      <c r="AQ89" t="n">
-        <v>0</v>
-      </c>
       <c r="AR89" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
     </row>
     <row r="90">
@@ -13629,19 +13617,19 @@
         <v>180</v>
       </c>
       <c r="AN90" t="n">
-        <v>301</v>
+        <v>51</v>
       </c>
       <c r="AO90" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AP90" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AQ90" t="n">
         <v>0</v>
       </c>
       <c r="AR90" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
     </row>
     <row r="91">
@@ -13775,19 +13763,19 @@
         <v>60</v>
       </c>
       <c r="AN91" t="n">
-        <v>399</v>
+        <v>127</v>
       </c>
       <c r="AO91" t="n">
         <v>0</v>
       </c>
       <c r="AP91" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AQ91" t="n">
         <v>0</v>
       </c>
       <c r="AR91" t="n">
-        <v>0</v>
+        <v>293</v>
       </c>
     </row>
     <row r="92">
@@ -13921,19 +13909,19 @@
         <v>80</v>
       </c>
       <c r="AN92" t="n">
-        <v>364</v>
+        <v>108</v>
       </c>
       <c r="AO92" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AP92" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AQ92" t="n">
         <v>0</v>
       </c>
       <c r="AR92" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
     </row>
     <row r="93">
@@ -14067,19 +14055,19 @@
         <v>190</v>
       </c>
       <c r="AN93" t="n">
-        <v>335</v>
+        <v>42</v>
       </c>
       <c r="AO93" t="n">
         <v>0</v>
       </c>
       <c r="AP93" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AQ93" t="n">
         <v>0</v>
       </c>
       <c r="AR93" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
     </row>
     <row r="94">
@@ -14213,10 +14201,10 @@
         <v>260</v>
       </c>
       <c r="AN94" t="n">
-        <v>373</v>
+        <v>164</v>
       </c>
       <c r="AO94" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="AP94" t="n">
         <v>4</v>
@@ -14225,7 +14213,7 @@
         <v>0</v>
       </c>
       <c r="AR94" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
     </row>
     <row r="95">
@@ -14359,19 +14347,19 @@
         <v>90</v>
       </c>
       <c r="AN95" t="n">
-        <v>356</v>
+        <v>47</v>
       </c>
       <c r="AO95" t="n">
         <v>0</v>
       </c>
       <c r="AP95" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="AQ95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR95" t="n">
-        <v>3</v>
+        <v>325</v>
       </c>
     </row>
     <row r="96">
@@ -14505,19 +14493,19 @@
         <v>90</v>
       </c>
       <c r="AN96" t="n">
-        <v>282</v>
+        <v>30</v>
       </c>
       <c r="AO96" t="n">
         <v>0</v>
       </c>
       <c r="AP96" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR96" t="n">
-        <v>1</v>
+        <v>247</v>
       </c>
     </row>
     <row r="97">
@@ -14651,19 +14639,19 @@
         <v>230</v>
       </c>
       <c r="AN97" t="n">
-        <v>378</v>
+        <v>21</v>
       </c>
       <c r="AO97" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="AP97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ97" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AR97" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="98">
@@ -14797,19 +14785,19 @@
         <v>0</v>
       </c>
       <c r="AN98" t="n">
-        <v>367</v>
+        <v>152</v>
       </c>
       <c r="AO98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP98" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="AQ98" t="n">
         <v>0</v>
       </c>
       <c r="AR98" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
     </row>
     <row r="99">
@@ -14943,19 +14931,19 @@
         <v>180</v>
       </c>
       <c r="AN99" t="n">
-        <v>321</v>
+        <v>87</v>
       </c>
       <c r="AO99" t="n">
         <v>0</v>
       </c>
       <c r="AP99" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR99" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
     </row>
     <row r="100">
@@ -15089,19 +15077,19 @@
         <v>90</v>
       </c>
       <c r="AN100" t="n">
-        <v>343</v>
+        <v>161</v>
       </c>
       <c r="AO100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP100" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR100" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="101">
@@ -15235,19 +15223,19 @@
         <v>40</v>
       </c>
       <c r="AN101" t="n">
-        <v>455</v>
+        <v>134</v>
       </c>
       <c r="AO101" t="n">
         <v>0</v>
       </c>
       <c r="AP101" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AQ101" t="n">
         <v>0</v>
       </c>
       <c r="AR101" t="n">
-        <v>0</v>
+        <v>281</v>
       </c>
     </row>
     <row r="102">
@@ -15278,7 +15266,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -15381,19 +15369,19 @@
         <v>160</v>
       </c>
       <c r="AN102" t="n">
-        <v>472</v>
+        <v>192</v>
       </c>
       <c r="AO102" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AP102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR102" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
     </row>
     <row r="103">
@@ -15527,19 +15515,19 @@
         <v>0</v>
       </c>
       <c r="AN103" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="AO103" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AP103" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AQ103" t="n">
         <v>0</v>
       </c>
       <c r="AR103" t="n">
-        <v>0</v>
+        <v>364</v>
       </c>
     </row>
     <row r="104">
@@ -15570,7 +15558,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -15673,19 +15661,19 @@
         <v>10</v>
       </c>
       <c r="AN104" t="n">
-        <v>422</v>
+        <v>139</v>
       </c>
       <c r="AO104" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AP104" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AR104" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
     </row>
     <row r="105">
@@ -15720,13 +15708,13 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>4100</v>
+        <v>4130</v>
       </c>
       <c r="H105" t="n">
-        <v>4150</v>
+        <v>4380</v>
       </c>
       <c r="I105" t="n">
-        <v>101.22</v>
+        <v>106.05</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -15738,7 +15726,7 @@
         <v>87</v>
       </c>
       <c r="M105" t="n">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="N105" t="n">
         <v>16</v>
@@ -15759,22 +15747,22 @@
         <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
       </c>
       <c r="V105" t="n">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="W105" t="n">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="X105" t="n">
         <v>87</v>
       </c>
       <c r="Y105" t="n">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="Z105" t="n">
         <v>16</v>
@@ -15795,43 +15783,43 @@
         <v>0</v>
       </c>
       <c r="AF105" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
       </c>
       <c r="AH105" t="n">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="AI105" t="n">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="AJ105" t="n">
-        <v>-930</v>
+        <v>-1130</v>
       </c>
       <c r="AK105" t="n">
         <v>70</v>
       </c>
       <c r="AL105" t="n">
-        <v>-930</v>
+        <v>-1130</v>
       </c>
       <c r="AM105" t="n">
         <v>70</v>
       </c>
       <c r="AN105" t="n">
-        <v>391</v>
+        <v>87</v>
       </c>
       <c r="AO105" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AP105" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AQ105" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AR105" t="n">
-        <v>5</v>
+        <v>350</v>
       </c>
     </row>
     <row r="106">
@@ -15965,19 +15953,19 @@
         <v>60</v>
       </c>
       <c r="AN106" t="n">
-        <v>366</v>
+        <v>113</v>
       </c>
       <c r="AO106" t="n">
         <v>1</v>
       </c>
       <c r="AP106" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="AQ106" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AR106" t="n">
-        <v>11</v>
+        <v>299</v>
       </c>
     </row>
     <row r="107">
@@ -16111,19 +16099,19 @@
         <v>60</v>
       </c>
       <c r="AN107" t="n">
-        <v>322</v>
+        <v>72</v>
       </c>
       <c r="AO107" t="n">
         <v>0</v>
       </c>
       <c r="AP107" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AQ107" t="n">
         <v>0</v>
       </c>
       <c r="AR107" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
     </row>
     <row r="108">
@@ -16257,19 +16245,19 @@
         <v>60</v>
       </c>
       <c r="AN108" t="n">
-        <v>324</v>
+        <v>32</v>
       </c>
       <c r="AO108" t="n">
         <v>0</v>
       </c>
       <c r="AP108" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AQ108" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AR108" t="n">
-        <v>5</v>
+        <v>304</v>
       </c>
     </row>
     <row r="109">
@@ -16403,10 +16391,10 @@
         <v>160</v>
       </c>
       <c r="AN109" t="n">
-        <v>407</v>
+        <v>193</v>
       </c>
       <c r="AO109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP109" t="n">
         <v>2</v>
@@ -16415,7 +16403,7 @@
         <v>0</v>
       </c>
       <c r="AR109" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
     </row>
     <row r="110">
@@ -16549,10 +16537,10 @@
         <v>0</v>
       </c>
       <c r="AN110" t="n">
-        <v>507</v>
+        <v>213</v>
       </c>
       <c r="AO110" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AP110" t="n">
         <v>0</v>
@@ -16561,7 +16549,7 @@
         <v>3</v>
       </c>
       <c r="AR110" t="n">
-        <v>2</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111">
@@ -16695,19 +16683,19 @@
         <v>110</v>
       </c>
       <c r="AN111" t="n">
-        <v>294</v>
+        <v>109</v>
       </c>
       <c r="AO111" t="n">
         <v>0</v>
       </c>
       <c r="AP111" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ111" t="n">
         <v>0</v>
       </c>
       <c r="AR111" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
     </row>
     <row r="112">
@@ -16841,19 +16829,19 @@
         <v>50</v>
       </c>
       <c r="AN112" t="n">
-        <v>403</v>
+        <v>178</v>
       </c>
       <c r="AO112" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AP112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR112" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
     </row>
     <row r="113">
@@ -16987,19 +16975,19 @@
         <v>130</v>
       </c>
       <c r="AN113" t="n">
-        <v>362</v>
+        <v>87</v>
       </c>
       <c r="AO113" t="n">
         <v>0</v>
       </c>
       <c r="AP113" t="n">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AR113" t="n">
-        <v>2</v>
+        <v>286</v>
       </c>
     </row>
     <row r="114">
@@ -17133,19 +17121,19 @@
         <v>0</v>
       </c>
       <c r="AN114" t="n">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="AO114" t="n">
         <v>0</v>
       </c>
       <c r="AP114" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AQ114" t="n">
         <v>0</v>
       </c>
       <c r="AR114" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
     </row>
     <row r="115">
@@ -17279,19 +17267,19 @@
         <v>110</v>
       </c>
       <c r="AN115" t="n">
-        <v>344</v>
+        <v>162</v>
       </c>
       <c r="AO115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ115" t="n">
         <v>0</v>
       </c>
       <c r="AR115" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="116">
@@ -17425,60 +17413,60 @@
         <v>20</v>
       </c>
       <c r="AN116" t="n">
-        <v>333</v>
+        <v>102</v>
       </c>
       <c r="AO116" t="n">
         <v>0</v>
       </c>
       <c r="AP116" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="AQ116" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AR116" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>stivfrancois@gmail.com</t>
+          <t>srirahayudurumias@gmail.com</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Fresly Jeica Manangkoda</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>fmanangkoda12@gmail.com</t>
+          <t>hmanabung01@gmail.com</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>(050) TAMAKO</t>
+          <t>(110) KENDAHE</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>3650</v>
+        <v>2610</v>
       </c>
       <c r="H117" t="n">
-        <v>3720</v>
+        <v>1940</v>
       </c>
       <c r="I117" t="n">
-        <v>101.92</v>
+        <v>74.33</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -17487,25 +17475,25 @@
         <v>0</v>
       </c>
       <c r="L117" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="M117" t="n">
-        <v>320</v>
+        <v>149</v>
       </c>
       <c r="N117" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -17517,31 +17505,31 @@
         <v>0</v>
       </c>
       <c r="V117" t="n">
-        <v>435</v>
+        <v>289</v>
       </c>
       <c r="W117" t="n">
-        <v>371</v>
+        <v>194</v>
       </c>
       <c r="X117" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="Y117" t="n">
-        <v>320</v>
+        <v>149</v>
       </c>
       <c r="Z117" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
       </c>
       <c r="AD117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE117" t="n">
         <v>0</v>
@@ -17553,93 +17541,93 @@
         <v>0</v>
       </c>
       <c r="AH117" t="n">
-        <v>435</v>
+        <v>289</v>
       </c>
       <c r="AI117" t="n">
-        <v>371</v>
+        <v>194</v>
       </c>
       <c r="AJ117" t="n">
-        <v>-700</v>
+        <v>-280</v>
       </c>
       <c r="AK117" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL117" t="n">
-        <v>-700</v>
+        <v>-280</v>
       </c>
       <c r="AM117" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AN117" t="n">
-        <v>364</v>
+        <v>95</v>
       </c>
       <c r="AO117" t="n">
         <v>0</v>
       </c>
       <c r="AP117" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AQ117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR117" t="n">
-        <v>6</v>
+        <v>149</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sulastri Bawenti</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>sulastribwnti@gmail.com</t>
+          <t>stivfrancois@gmail.com</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sutrisno Sariang</t>
+          <t>Fresly Jeica Manangkoda</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>sutrisnosariang90@gmail.com</t>
+          <t>fmanangkoda12@gmail.com</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>(100) TABUKAN UTARA</t>
+          <t>(050) TAMAKO</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>3750</v>
+        <v>3650</v>
       </c>
       <c r="H118" t="n">
-        <v>4200</v>
+        <v>3720</v>
       </c>
       <c r="I118" t="n">
-        <v>112</v>
+        <v>101.92</v>
       </c>
       <c r="J118" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="L118" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="M118" t="n">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -17660,22 +17648,22 @@
         <v>42</v>
       </c>
       <c r="U118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V118" t="n">
-        <v>537</v>
+        <v>435</v>
       </c>
       <c r="W118" t="n">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="X118" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="Y118" t="n">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="Z118" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -17696,96 +17684,96 @@
         <v>42</v>
       </c>
       <c r="AG118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH118" t="n">
-        <v>537</v>
+        <v>435</v>
       </c>
       <c r="AI118" t="n">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="AJ118" t="n">
-        <v>-1620</v>
+        <v>-700</v>
       </c>
       <c r="AK118" t="n">
-        <v>170</v>
+        <v>10</v>
       </c>
       <c r="AL118" t="n">
-        <v>-1620</v>
+        <v>-700</v>
       </c>
       <c r="AM118" t="n">
-        <v>170</v>
+        <v>10</v>
       </c>
       <c r="AN118" t="n">
-        <v>378</v>
+        <v>64</v>
       </c>
       <c r="AO118" t="n">
         <v>0</v>
       </c>
       <c r="AP118" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AQ118" t="n">
         <v>0</v>
       </c>
       <c r="AR118" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Sulastri Bawenti</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>sunarditamado2@gmail.com</t>
+          <t>sulastribwnti@gmail.com</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Sutrisno Sariang</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>stevenmanoppo36@gmail.com</t>
+          <t>sutrisnosariang90@gmail.com</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>(040) MANGANITU SELATAN</t>
+          <t>(100) TABUKAN UTARA</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>4280</v>
+        <v>3750</v>
       </c>
       <c r="H119" t="n">
-        <v>4480</v>
+        <v>4200</v>
       </c>
       <c r="I119" t="n">
-        <v>104.67</v>
+        <v>112</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="L119" t="n">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="M119" t="n">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="N119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -17797,31 +17785,31 @@
         <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
       </c>
       <c r="T119" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="U119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V119" t="n">
-        <v>486</v>
+        <v>537</v>
       </c>
       <c r="W119" t="n">
-        <v>442</v>
+        <v>403</v>
       </c>
       <c r="X119" t="n">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="Y119" t="n">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="Z119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -17833,90 +17821,90 @@
         <v>0</v>
       </c>
       <c r="AD119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
       </c>
       <c r="AF119" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="AG119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH119" t="n">
-        <v>486</v>
+        <v>537</v>
       </c>
       <c r="AI119" t="n">
-        <v>442</v>
+        <v>403</v>
       </c>
       <c r="AJ119" t="n">
-        <v>-580</v>
+        <v>-1620</v>
       </c>
       <c r="AK119" t="n">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="AL119" t="n">
-        <v>-580</v>
+        <v>-1620</v>
       </c>
       <c r="AM119" t="n">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="AN119" t="n">
-        <v>420</v>
+        <v>134</v>
       </c>
       <c r="AO119" t="n">
         <v>0</v>
       </c>
       <c r="AP119" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AQ119" t="n">
         <v>0</v>
       </c>
       <c r="AR119" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>tangkabiringananti@gmail.com</t>
+          <t>sunarditamado2@gmail.com</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>hmanabung01@gmail.com</t>
+          <t>stevenmanoppo36@gmail.com</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>(110) KENDAHE</t>
+          <t>(040) MANGANITU SELATAN</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>4220</v>
+        <v>4280</v>
       </c>
       <c r="H120" t="n">
-        <v>3790</v>
+        <v>4480</v>
       </c>
       <c r="I120" t="n">
-        <v>89.81</v>
+        <v>104.67</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -17925,13 +17913,13 @@
         <v>0</v>
       </c>
       <c r="L120" t="n">
-        <v>164</v>
+        <v>44</v>
       </c>
       <c r="M120" t="n">
-        <v>266</v>
+        <v>378</v>
       </c>
       <c r="N120" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -17943,31 +17931,31 @@
         <v>0</v>
       </c>
       <c r="R120" t="n">
+        <v>1</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
+        <v>58</v>
+      </c>
+      <c r="U120" t="n">
         <v>3</v>
       </c>
-      <c r="S120" t="n">
-        <v>0</v>
-      </c>
-      <c r="T120" t="n">
-        <v>96</v>
-      </c>
-      <c r="U120" t="n">
-        <v>0</v>
-      </c>
       <c r="V120" t="n">
-        <v>544</v>
+        <v>486</v>
       </c>
       <c r="W120" t="n">
-        <v>380</v>
+        <v>442</v>
       </c>
       <c r="X120" t="n">
-        <v>164</v>
+        <v>44</v>
       </c>
       <c r="Y120" t="n">
-        <v>266</v>
+        <v>378</v>
       </c>
       <c r="Z120" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -17979,108 +17967,108 @@
         <v>0</v>
       </c>
       <c r="AD120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>58</v>
+      </c>
+      <c r="AG120" t="n">
         <v>3</v>
       </c>
-      <c r="AE120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF120" t="n">
-        <v>96</v>
-      </c>
-      <c r="AG120" t="n">
-        <v>0</v>
-      </c>
       <c r="AH120" t="n">
-        <v>544</v>
+        <v>486</v>
       </c>
       <c r="AI120" t="n">
-        <v>380</v>
+        <v>442</v>
       </c>
       <c r="AJ120" t="n">
-        <v>-1220</v>
+        <v>-580</v>
       </c>
       <c r="AK120" t="n">
-        <v>-10</v>
+        <v>60</v>
       </c>
       <c r="AL120" t="n">
-        <v>-1220</v>
+        <v>-580</v>
       </c>
       <c r="AM120" t="n">
-        <v>-10</v>
+        <v>60</v>
       </c>
       <c r="AN120" t="n">
-        <v>430</v>
+        <v>44</v>
       </c>
       <c r="AO120" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AP120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ120" t="n">
         <v>0</v>
       </c>
       <c r="AR120" t="n">
-        <v>0</v>
+        <v>378</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ambrosius Tampi Tangkabiringan</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>tangkabiringanayen70@gmail.com</t>
+          <t>tangkabiringananti@gmail.com</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>georgemulersasiangsasiang@gmail.com</t>
+          <t>hmanabung01@gmail.com</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(110) KENDAHE</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="G121" t="n">
+        <v>4220</v>
+      </c>
+      <c r="H121" t="n">
         <v>3790</v>
       </c>
-      <c r="H121" t="n">
-        <v>3230</v>
-      </c>
       <c r="I121" t="n">
-        <v>85.22</v>
+        <v>89.81</v>
       </c>
       <c r="J121" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="L121" t="n">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="M121" t="n">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="N121" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P121" t="n">
         <v>0</v>
@@ -18089,34 +18077,34 @@
         <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
       </c>
       <c r="T121" t="n">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="U121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V121" t="n">
-        <v>479</v>
+        <v>544</v>
       </c>
       <c r="W121" t="n">
-        <v>292</v>
+        <v>380</v>
       </c>
       <c r="X121" t="n">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="Y121" t="n">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="Z121" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AA121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
         <v>0</v>
@@ -18125,108 +18113,108 @@
         <v>0</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
       </c>
       <c r="AF121" t="n">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="AG121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH121" t="n">
-        <v>479</v>
+        <v>544</v>
       </c>
       <c r="AI121" t="n">
-        <v>292</v>
+        <v>380</v>
       </c>
       <c r="AJ121" t="n">
-        <v>-1000</v>
+        <v>-1220</v>
       </c>
       <c r="AK121" t="n">
-        <v>310</v>
+        <v>-10</v>
       </c>
       <c r="AL121" t="n">
-        <v>-1000</v>
+        <v>-1220</v>
       </c>
       <c r="AM121" t="n">
-        <v>310</v>
+        <v>-10</v>
       </c>
       <c r="AN121" t="n">
-        <v>379</v>
+        <v>164</v>
       </c>
       <c r="AO121" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AP121" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AQ121" t="n">
         <v>0</v>
       </c>
       <c r="AR121" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Ambrosius Tampi Tangkabiringan</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>tentangsangihe@gmail.com</t>
+          <t>tangkabiringanayen70@gmail.com</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>hmanabung01@gmail.com</t>
+          <t>georgemulersasiangsasiang@gmail.com</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>(110) KENDAHE</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>4080</v>
+        <v>3790</v>
       </c>
       <c r="H122" t="n">
-        <v>3710</v>
+        <v>3230</v>
       </c>
       <c r="I122" t="n">
-        <v>90.93000000000001</v>
+        <v>85.22</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="L122" t="n">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="M122" t="n">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="N122" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
@@ -18235,34 +18223,34 @@
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
       </c>
       <c r="T122" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="U122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V122" t="n">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="W122" t="n">
-        <v>359</v>
+        <v>292</v>
       </c>
       <c r="X122" t="n">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="Y122" t="n">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="Z122" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB122" t="n">
         <v>0</v>
@@ -18271,216 +18259,216 @@
         <v>0</v>
       </c>
       <c r="AD122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE122" t="n">
         <v>0</v>
       </c>
       <c r="AF122" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="AG122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH122" t="n">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="AI122" t="n">
-        <v>359</v>
+        <v>292</v>
       </c>
       <c r="AJ122" t="n">
-        <v>-770</v>
+        <v>-1000</v>
       </c>
       <c r="AK122" t="n">
-        <v>120</v>
+        <v>310</v>
       </c>
       <c r="AL122" t="n">
-        <v>-770</v>
+        <v>-1000</v>
       </c>
       <c r="AM122" t="n">
-        <v>120</v>
+        <v>310</v>
       </c>
       <c r="AN122" t="n">
-        <v>419</v>
+        <v>185</v>
       </c>
       <c r="AO122" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AP122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ122" t="n">
         <v>0</v>
       </c>
       <c r="AR122" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>tianfirnanda16@gmail.com</t>
+          <t>tentangsangihe@gmail.com</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ivonne Lariunaung</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>vonnelariunaung77560@gmail.com</t>
+          <t>hmanabung01@gmail.com</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>(091) TAHUNA TIMUR</t>
+          <t>(110) KENDAHE</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>4420</v>
+        <v>4080</v>
       </c>
       <c r="H123" t="n">
-        <v>4120</v>
+        <v>3710</v>
       </c>
       <c r="I123" t="n">
-        <v>93.20999999999999</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="J123" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="L123" t="n">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="M123" t="n">
-        <v>338</v>
+        <v>256</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
       </c>
       <c r="T123" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="U123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V123" t="n">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="W123" t="n">
-        <v>398</v>
+        <v>359</v>
       </c>
       <c r="X123" t="n">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="Y123" t="n">
-        <v>338</v>
+        <v>256</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AA123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
       </c>
       <c r="AD123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE123" t="n">
         <v>0</v>
       </c>
       <c r="AF123" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="AG123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH123" t="n">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="AI123" t="n">
-        <v>398</v>
+        <v>359</v>
       </c>
       <c r="AJ123" t="n">
-        <v>-560</v>
+        <v>-770</v>
       </c>
       <c r="AK123" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AL123" t="n">
-        <v>-560</v>
+        <v>-770</v>
       </c>
       <c r="AM123" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AN123" t="n">
-        <v>432</v>
+        <v>126</v>
       </c>
       <c r="AO123" t="n">
         <v>0</v>
       </c>
       <c r="AP123" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AQ123" t="n">
         <v>0</v>
       </c>
       <c r="AR123" t="n">
-        <v>3</v>
+        <v>256</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>tikamustika1704@gmail.com</t>
+          <t>tianfirnanda16@gmail.com</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>jeniemonok7@gmail.com</t>
+          <t>vonnelariunaung77560@gmail.com</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -18494,34 +18482,34 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>4420</v>
+        <v>4520</v>
       </c>
       <c r="H124" t="n">
-        <v>3720</v>
+        <v>3860</v>
       </c>
       <c r="I124" t="n">
-        <v>84.16</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="J124" t="n">
         <v>10</v>
       </c>
       <c r="K124" t="n">
-        <v>0.85</v>
+        <v>1.27</v>
       </c>
       <c r="L124" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="M124" t="n">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="N124" t="n">
         <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
@@ -18533,31 +18521,31 @@
         <v>0</v>
       </c>
       <c r="T124" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="U124" t="n">
         <v>1</v>
       </c>
       <c r="V124" t="n">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="W124" t="n">
         <v>371</v>
       </c>
       <c r="X124" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="Y124" t="n">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="Z124" t="n">
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -18569,102 +18557,102 @@
         <v>0</v>
       </c>
       <c r="AF124" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="AG124" t="n">
         <v>1</v>
       </c>
       <c r="AH124" t="n">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="AI124" t="n">
         <v>371</v>
       </c>
       <c r="AJ124" t="n">
-        <v>-720</v>
+        <v>-540</v>
       </c>
       <c r="AK124" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="AL124" t="n">
-        <v>-720</v>
+        <v>-540</v>
       </c>
       <c r="AM124" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="AN124" t="n">
-        <v>437</v>
+        <v>128</v>
       </c>
       <c r="AO124" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AP124" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR124" t="n">
-        <v>0</v>
+        <v>332</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Kristia Mirnawati Tumpias</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>tumpiask@gmail.com</t>
+          <t>tikamustika1704@gmail.com</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>stevenmanoppo36@gmail.com</t>
+          <t>jeniemonok7@gmail.com</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>(040) MANGANITU SELATAN</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>3030</v>
+        <v>4420</v>
       </c>
       <c r="H125" t="n">
         <v>3720</v>
       </c>
       <c r="I125" t="n">
-        <v>122.77</v>
+        <v>84.16</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K125" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="M125" t="n">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="N125" t="n">
         <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P125" t="n">
         <v>0</v>
@@ -18673,126 +18661,126 @@
         <v>0</v>
       </c>
       <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>44</v>
+      </c>
+      <c r="U125" t="n">
+        <v>1</v>
+      </c>
+      <c r="V125" t="n">
+        <v>514</v>
+      </c>
+      <c r="W125" t="n">
+        <v>371</v>
+      </c>
+      <c r="X125" t="n">
+        <v>141</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>326</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA125" t="n">
         <v>2</v>
       </c>
-      <c r="S125" t="n">
-        <v>1</v>
-      </c>
-      <c r="T125" t="n">
-        <v>79</v>
-      </c>
-      <c r="U125" t="n">
+      <c r="AB125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>514</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>371</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>-720</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>-720</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>141</v>
+      </c>
+      <c r="AO125" t="n">
         <v>2</v>
       </c>
-      <c r="V125" t="n">
-        <v>372</v>
-      </c>
-      <c r="W125" t="n">
-        <v>372</v>
-      </c>
-      <c r="X125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y125" t="n">
-        <v>288</v>
-      </c>
-      <c r="Z125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD125" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE125" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF125" t="n">
-        <v>79</v>
-      </c>
-      <c r="AG125" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH125" t="n">
-        <v>372</v>
-      </c>
-      <c r="AI125" t="n">
-        <v>372</v>
-      </c>
-      <c r="AJ125" t="n">
-        <v>-690</v>
-      </c>
-      <c r="AK125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL125" t="n">
-        <v>-690</v>
-      </c>
-      <c r="AM125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN125" t="n">
-        <v>303</v>
-      </c>
-      <c r="AO125" t="n">
-        <v>0</v>
-      </c>
       <c r="AP125" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AQ125" t="n">
         <v>0</v>
       </c>
       <c r="AR125" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Don Albert Seimahuira</t>
+          <t>Kristia Mirnawati Tumpias</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ungkealbert39@gmail.com</t>
+          <t>tumpiask@gmail.com</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ferdinandtangkabiringan@gmail.com</t>
+          <t>stevenmanoppo36@gmail.com</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(040) MANGANITU SELATAN</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>3640</v>
+        <v>3030</v>
       </c>
       <c r="H126" t="n">
-        <v>3470</v>
+        <v>3720</v>
       </c>
       <c r="I126" t="n">
-        <v>95.33</v>
+        <v>122.77</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -18801,144 +18789,144 @@
         <v>0</v>
       </c>
       <c r="L126" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
         <v>2</v>
       </c>
-      <c r="O126" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" t="n">
-        <v>1</v>
-      </c>
       <c r="S126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T126" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="U126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V126" t="n">
-        <v>441</v>
+        <v>372</v>
       </c>
       <c r="W126" t="n">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="X126" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="Z126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD126" t="n">
         <v>2</v>
       </c>
-      <c r="AA126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD126" t="n">
-        <v>1</v>
-      </c>
       <c r="AE126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF126" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="AG126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH126" t="n">
-        <v>441</v>
+        <v>372</v>
       </c>
       <c r="AI126" t="n">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="AJ126" t="n">
-        <v>-770</v>
+        <v>-690</v>
       </c>
       <c r="AK126" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AL126" t="n">
-        <v>-770</v>
+        <v>-690</v>
       </c>
       <c r="AM126" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AN126" t="n">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="AO126" t="n">
         <v>0</v>
       </c>
       <c r="AP126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AQ126" t="n">
         <v>0</v>
       </c>
       <c r="AR126" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Don Albert Seimahuira</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>verawaticristylolaroh02@gmail.com</t>
+          <t>ungkealbert39@gmail.com</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Ferdinand Tangkabiringan</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>jeniemonok7@gmail.com</t>
+          <t>ferdinandtangkabiringan@gmail.com</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>(091) TAHUNA TIMUR</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H127" t="n">
-        <v>3540</v>
+        <v>3470</v>
       </c>
       <c r="I127" t="n">
-        <v>88.5</v>
+        <v>95.33</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -18947,165 +18935,165 @@
         <v>0</v>
       </c>
       <c r="L127" t="n">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="M127" t="n">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="N127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O127" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="P127" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
         <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
       </c>
       <c r="T127" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="U127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V127" t="n">
-        <v>505</v>
+        <v>441</v>
       </c>
       <c r="W127" t="n">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="X127" t="n">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="Y127" t="n">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="Z127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA127" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
       </c>
       <c r="AD127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE127" t="n">
         <v>0</v>
       </c>
       <c r="AF127" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="AG127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH127" t="n">
-        <v>505</v>
+        <v>441</v>
       </c>
       <c r="AI127" t="n">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AJ127" t="n">
-        <v>-1050</v>
+        <v>-770</v>
       </c>
       <c r="AK127" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="AL127" t="n">
-        <v>-1050</v>
+        <v>-770</v>
       </c>
       <c r="AM127" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="AN127" t="n">
-        <v>394</v>
+        <v>101</v>
       </c>
       <c r="AO127" t="n">
         <v>0</v>
       </c>
       <c r="AP127" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AQ127" t="n">
         <v>0</v>
       </c>
       <c r="AR127" t="n">
-        <v>1</v>
+        <v>306</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>wenaserin@gmail.com</t>
+          <t>verawaticristylolaroh02@gmail.com</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>georgemulersasiangsasiang@gmail.com</t>
+          <t>jeniemonok7@gmail.com</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>3820</v>
+        <v>4000</v>
       </c>
       <c r="H128" t="n">
-        <v>3550</v>
+        <v>3540</v>
       </c>
       <c r="I128" t="n">
-        <v>92.93000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="J128" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="L128" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="M128" t="n">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="N128" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O128" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="P128" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q128" t="n">
         <v>0</v>
@@ -19117,31 +19105,31 @@
         <v>0</v>
       </c>
       <c r="T128" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
       </c>
       <c r="V128" t="n">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="W128" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="X128" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="Y128" t="n">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="Z128" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA128" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="AB128" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -19153,105 +19141,105 @@
         <v>0</v>
       </c>
       <c r="AF128" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
       </c>
       <c r="AH128" t="n">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="AI128" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AJ128" t="n">
-        <v>-990</v>
+        <v>-1050</v>
       </c>
       <c r="AK128" t="n">
         <v>180</v>
       </c>
       <c r="AL128" t="n">
-        <v>-990</v>
+        <v>-1050</v>
       </c>
       <c r="AM128" t="n">
         <v>180</v>
       </c>
       <c r="AN128" t="n">
-        <v>372</v>
+        <v>142</v>
       </c>
       <c r="AO128" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AP128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AQ128" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AR128" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>windametia67@gmail.com</t>
+          <t>wenaserin@gmail.com</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Jeferson Manahampi</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>manahampijeferson94@gmail.com</t>
+          <t>georgemulersasiangsasiang@gmail.com</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>(040) MANGANITU SELATAN</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>3180</v>
+        <v>3820</v>
       </c>
       <c r="H129" t="n">
-        <v>3080</v>
+        <v>3550</v>
       </c>
       <c r="I129" t="n">
-        <v>96.86</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K129" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="L129" t="n">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="M129" t="n">
-        <v>187</v>
+        <v>317</v>
       </c>
       <c r="N129" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O129" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q129" t="n">
         <v>0</v>
@@ -19263,100 +19251,100 @@
         <v>0</v>
       </c>
       <c r="T129" t="n">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="U129" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V129" t="n">
-        <v>360</v>
+        <v>481</v>
       </c>
       <c r="W129" t="n">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="X129" t="n">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="Y129" t="n">
-        <v>189</v>
+        <v>317</v>
       </c>
       <c r="Z129" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
       </c>
       <c r="AD129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE129" t="n">
         <v>0</v>
       </c>
       <c r="AF129" t="n">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="AG129" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH129" t="n">
-        <v>360</v>
+        <v>481</v>
       </c>
       <c r="AI129" t="n">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="AJ129" t="n">
-        <v>-420</v>
+        <v>-990</v>
       </c>
       <c r="AK129" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="AL129" t="n">
-        <v>-420</v>
+        <v>-990</v>
       </c>
       <c r="AM129" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="AN129" t="n">
-        <v>313</v>
+        <v>131</v>
       </c>
       <c r="AO129" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AP129" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AQ129" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AR129" t="n">
-        <v>1</v>
+        <v>317</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ybawembang@gmail.com</t>
+          <t>windametia67@gmail.com</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Jeferson Manahampi</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>stevenmanoppo36@gmail.com</t>
+          <t>manahampijeferson94@gmail.com</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -19370,13 +19358,13 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>3910</v>
+        <v>3180</v>
       </c>
       <c r="H130" t="n">
-        <v>3540</v>
+        <v>3080</v>
       </c>
       <c r="I130" t="n">
-        <v>90.54000000000001</v>
+        <v>96.86</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -19385,19 +19373,19 @@
         <v>0</v>
       </c>
       <c r="L130" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M130" t="n">
-        <v>307</v>
+        <v>187</v>
       </c>
       <c r="N130" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O130" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q130" t="n">
         <v>0</v>
@@ -19409,28 +19397,28 @@
         <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="U130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V130" t="n">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="W130" t="n">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="X130" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="Y130" t="n">
-        <v>307</v>
+        <v>189</v>
       </c>
       <c r="Z130" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AA130" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
         <v>0</v>
@@ -19439,90 +19427,90 @@
         <v>0</v>
       </c>
       <c r="AD130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE130" t="n">
         <v>0</v>
       </c>
       <c r="AF130" t="n">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="AG130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH130" t="n">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="AI130" t="n">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="AJ130" t="n">
-        <v>-560</v>
+        <v>-420</v>
       </c>
       <c r="AK130" t="n">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="AL130" t="n">
-        <v>-560</v>
+        <v>-420</v>
       </c>
       <c r="AM130" t="n">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="AN130" t="n">
-        <v>386</v>
+        <v>59</v>
       </c>
       <c r="AO130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP130" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AQ130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR130" t="n">
-        <v>1</v>
+        <v>187</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>yudhistiratangkabiringan@gmail.com</t>
+          <t>ybawembang@gmail.com</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ferdinandtangkabiringan@gmail.com</t>
+          <t>stevenmanoppo36@gmail.com</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(040) MANGANITU SELATAN</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>3810</v>
+        <v>3910</v>
       </c>
       <c r="H131" t="n">
-        <v>2640</v>
+        <v>3540</v>
       </c>
       <c r="I131" t="n">
-        <v>69.29000000000001</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -19531,16 +19519,16 @@
         <v>0</v>
       </c>
       <c r="L131" t="n">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="M131" t="n">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="N131" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="P131" t="n">
         <v>0</v>
@@ -19555,28 +19543,28 @@
         <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="U131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V131" t="n">
-        <v>400</v>
+        <v>447</v>
       </c>
       <c r="W131" t="n">
-        <v>261</v>
+        <v>334</v>
       </c>
       <c r="X131" t="n">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="Y131" t="n">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="Z131" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AB131" t="n">
         <v>0</v>
@@ -19591,189 +19579,335 @@
         <v>0</v>
       </c>
       <c r="AF131" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AG131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH131" t="n">
-        <v>400</v>
+        <v>447</v>
       </c>
       <c r="AI131" t="n">
-        <v>261</v>
+        <v>334</v>
       </c>
       <c r="AJ131" t="n">
-        <v>-190</v>
+        <v>-560</v>
       </c>
       <c r="AK131" t="n">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="AL131" t="n">
-        <v>-190</v>
+        <v>-560</v>
       </c>
       <c r="AM131" t="n">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="AN131" t="n">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="AO131" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="AP131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ131" t="n">
         <v>0</v>
       </c>
       <c r="AR131" t="n">
-        <v>0</v>
+        <v>307</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>yudhistiratangkabiringan@gmail.com</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Ferdinand Tangkabiringan</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ferdinandtangkabiringan@gmail.com</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>(090) TAHUNA</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Yetty</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>3810</v>
+      </c>
+      <c r="H132" t="n">
+        <v>2640</v>
+      </c>
+      <c r="I132" t="n">
+        <v>69.29000000000001</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>139</v>
+      </c>
+      <c r="M132" t="n">
+        <v>209</v>
+      </c>
+      <c r="N132" t="n">
+        <v>6</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" t="n">
+        <v>46</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0</v>
+      </c>
+      <c r="V132" t="n">
+        <v>400</v>
+      </c>
+      <c r="W132" t="n">
+        <v>261</v>
+      </c>
+      <c r="X132" t="n">
+        <v>139</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>209</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>400</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>261</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>-190</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>-190</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>30</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>139</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
           <t>Yustin Durian</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>yustindurian@gmail.com</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>Fiane Greti Mansauda</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>fianemansauda89@gmail.com</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E133" t="inlineStr">
         <is>
           <t>(070) TABUKAN TENGAH</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>Kharis</t>
         </is>
       </c>
-      <c r="G132" t="n">
+      <c r="G133" t="n">
         <v>3400</v>
       </c>
-      <c r="H132" t="n">
+      <c r="H133" t="n">
         <v>3340</v>
       </c>
-      <c r="I132" t="n">
+      <c r="I133" t="n">
         <v>98.23999999999999</v>
       </c>
-      <c r="J132" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" t="n">
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
         <v>131</v>
       </c>
-      <c r="M132" t="n">
+      <c r="M133" t="n">
         <v>278</v>
       </c>
-      <c r="N132" t="n">
+      <c r="N133" t="n">
         <v>2</v>
       </c>
-      <c r="O132" t="n">
-        <v>0</v>
-      </c>
-      <c r="P132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
-      <c r="R132" t="n">
-        <v>1</v>
-      </c>
-      <c r="S132" t="n">
-        <v>0</v>
-      </c>
-      <c r="T132" t="n">
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>1</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
         <v>43</v>
       </c>
-      <c r="U132" t="n">
-        <v>1</v>
-      </c>
-      <c r="V132" t="n">
+      <c r="U133" t="n">
+        <v>1</v>
+      </c>
+      <c r="V133" t="n">
         <v>456</v>
       </c>
-      <c r="W132" t="n">
+      <c r="W133" t="n">
         <v>325</v>
       </c>
-      <c r="X132" t="n">
+      <c r="X133" t="n">
         <v>131</v>
       </c>
-      <c r="Y132" t="n">
+      <c r="Y133" t="n">
         <v>278</v>
       </c>
-      <c r="Z132" t="n">
+      <c r="Z133" t="n">
         <v>2</v>
       </c>
-      <c r="AA132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF132" t="n">
+      <c r="AA133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF133" t="n">
         <v>43</v>
       </c>
-      <c r="AG132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH132" t="n">
+      <c r="AG133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH133" t="n">
         <v>456</v>
       </c>
-      <c r="AI132" t="n">
+      <c r="AI133" t="n">
         <v>325</v>
       </c>
-      <c r="AJ132" t="n">
+      <c r="AJ133" t="n">
         <v>-1160</v>
       </c>
-      <c r="AK132" t="n">
+      <c r="AK133" t="n">
         <v>90</v>
       </c>
-      <c r="AL132" t="n">
+      <c r="AL133" t="n">
         <v>-1160</v>
       </c>
-      <c r="AM132" t="n">
+      <c r="AM133" t="n">
         <v>90</v>
       </c>
-      <c r="AN132" t="n">
-        <v>368</v>
-      </c>
-      <c r="AO132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP132" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR132" t="n">
-        <v>0</v>
+      <c r="AN133" t="n">
+        <v>131</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>278</v>
       </c>
     </row>
   </sheetData>
